--- a/nr-update-fr-core-dependency/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/nr-update-fr-core-dependency/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T14:52:43+00:00</t>
+    <t>2024-04-03T13:38:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-fr-core-dependency/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/nr-update-fr-core-dependency/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-3</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T13:38:42+00:00</t>
+    <t>2024-04-03T14:06:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -686,7 +686,7 @@
     <t>numAutorisationArhgos</t>
   </si>
   <si>
-    <t>Identifiant fonctionnel, numéro d'autorisation ARHGOS (numeroAutorisationARHGOS).</t>
+    <t>Identifiant fonctionnel, numéro d'autorisation ARHGOS (numeroAutorisationARHGOS). Le system est mis à titre indicatif et pourra évoluer.</t>
   </si>
   <si>
     <t>HealthcareService.identifier:numAutorisationArhgos.id</t>
@@ -783,7 +783,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>https://arhgos.ars.sante.fr/</t>
+    <t>https://arhgos.ars.sante.fr</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
